--- a/righe_Ordini_ARCA.xlsx
+++ b/righe_Ordini_ARCA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5AF027-B607-479A-90B4-371304675B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6081871-7941-48C5-A8FB-B8EB6C83C7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{20AF6118-56C4-42BC-B769-79C778699C55}"/>
   </bookViews>
@@ -2836,7 +2836,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Denis Venezian" refreshedDate="46277.354288078706" backgroundQuery="1" createdVersion="1" refreshedVersion="8" recordCount="914" xr:uid="{305E6FD6-A5B9-4639-B69A-A273DE604CA6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Denis Venezian" refreshedDate="46279.354263541667" backgroundQuery="1" createdVersion="1" refreshedVersion="8" recordCount="914" xr:uid="{305E6FD6-A5B9-4639-B69A-A273DE604CA6}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="9">
     <cacheField name="Codice Documento" numFmtId="0" sqlType="1">

--- a/righe_Ordini_ARCA.xlsx
+++ b/righe_Ordini_ARCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17026A13-EF4E-44EB-AC07-1560CB9C6307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED564299-EF83-43D4-9644-C6EB0AD60400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3375" yWindow="4500" windowWidth="22935" windowHeight="11100" xr2:uid="{20AF6118-56C4-42BC-B769-79C778699C55}"/>
   </bookViews>
@@ -3214,7 +3214,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Denis Venezian" refreshedDate="46291.354291087962" backgroundQuery="1" createdVersion="1" refreshedVersion="8" recordCount="926" xr:uid="{305E6FD6-A5B9-4639-B69A-A273DE604CA6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Denis Venezian" refreshedDate="46293.354243518515" backgroundQuery="1" createdVersion="1" refreshedVersion="8" recordCount="926" xr:uid="{305E6FD6-A5B9-4639-B69A-A273DE604CA6}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="9">
     <cacheField name="Codice Documento" numFmtId="0" sqlType="1">

--- a/righe_Ordini_ARCA.xlsx
+++ b/righe_Ordini_ARCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A860C976-9F01-4C09-B236-2D3AA148C9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F37C41F-BF65-4E2E-8120-46389FEF491A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{20AF6118-56C4-42BC-B769-79C778699C55}"/>
   </bookViews>
@@ -3157,7 +3157,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Denis Venezian" refreshedDate="46298.354286805552" backgroundQuery="1" createdVersion="1" refreshedVersion="8" recordCount="970" xr:uid="{305E6FD6-A5B9-4639-B69A-A273DE604CA6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Denis Venezian" refreshedDate="46300.354248611111" backgroundQuery="1" createdVersion="1" refreshedVersion="8" recordCount="970" xr:uid="{305E6FD6-A5B9-4639-B69A-A273DE604CA6}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="9">
     <cacheField name="Codice Documento" numFmtId="0" sqlType="1">

--- a/righe_Ordini_ARCA.xlsx
+++ b/righe_Ordini_ARCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E4C8C9-20D7-436B-805E-D46596FCA30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E09E32-62EB-485C-A093-1B13605F2194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{20AF6118-56C4-42BC-B769-79C778699C55}"/>
   </bookViews>
@@ -2809,7 +2809,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Denis Venezian" refreshedDate="46325.354266550923" backgroundQuery="1" createdVersion="1" refreshedVersion="8" recordCount="934" xr:uid="{305E6FD6-A5B9-4639-B69A-A273DE604CA6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Denis Venezian" refreshedDate="46326.354293518518" backgroundQuery="1" createdVersion="1" refreshedVersion="8" recordCount="934" xr:uid="{305E6FD6-A5B9-4639-B69A-A273DE604CA6}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="9">
     <cacheField name="Codice Documento" numFmtId="0" sqlType="1">
